--- a/Database/Cecafe Economics.xlsx
+++ b/Database/Cecafe Economics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://etgworld.sharepoint.com/sites/SoftsDatabase/Shared Documents/Database/Hardmine/Fundamental/Cecafe Monthly/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{43F2D55E-6037-45EB-9D2C-E2BB70EA8F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9597A9CB-0DF3-46B2-8BE5-321948BEC98F}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="8_{43F2D55E-6037-45EB-9D2C-E2BB70EA8F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B18883B1-C34A-413E-B4A7-9A626CC2523C}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{EF03BD97-5382-4815-B896-D35D074F26AE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Date</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>Robusta Avg Price ($ per Bag)</t>
+  </si>
+  <si>
+    <t>Soluble Volume (60kg Bags)</t>
   </si>
 </sst>
 </file>
@@ -441,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8752819F-0DA7-4367-B00D-7576CB46EDD7}">
-  <dimension ref="A1:G437"/>
+  <dimension ref="A1:H437"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -451,7 +454,7 @@
     <col min="7" max="7" width="23.41796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -473,8 +476,11 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1">
         <v>32964</v>
       </c>
@@ -498,8 +504,11 @@
         <f>E2*1000/D2</f>
         <v>56.949594487055755</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H2">
+        <v>109949</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1">
         <v>32994</v>
       </c>
@@ -523,8 +532,11 @@
         <f t="shared" ref="G3:G66" si="1">E3*1000/D3</f>
         <v>50.787065049317619</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H3">
+        <v>339583</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1">
         <v>33025</v>
       </c>
@@ -548,8 +560,11 @@
         <f t="shared" si="1"/>
         <v>51.302560571850918</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H4">
+        <v>254316</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1">
         <v>33055</v>
       </c>
@@ -573,8 +588,11 @@
         <f t="shared" si="1"/>
         <v>48.292499957376435</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H5">
+        <v>145586</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1">
         <v>33086</v>
       </c>
@@ -598,8 +616,11 @@
         <f t="shared" si="1"/>
         <v>48.295764624727674</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H6">
+        <v>191129</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1">
         <v>33117</v>
       </c>
@@ -623,8 +644,11 @@
         <f t="shared" si="1"/>
         <v>51.817497659677308</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H7">
+        <v>225367</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1">
         <v>33147</v>
       </c>
@@ -648,8 +672,11 @@
         <f t="shared" si="1"/>
         <v>54.56405452707866</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H8">
+        <v>98808</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1">
         <v>33178</v>
       </c>
@@ -673,8 +700,11 @@
         <f t="shared" si="1"/>
         <v>54.749302000930662</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H9">
+        <v>246157</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1">
         <v>33208</v>
       </c>
@@ -698,8 +728,11 @@
         <f t="shared" si="1"/>
         <v>54.30657442306061</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H10">
+        <v>163686</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1">
         <v>33239</v>
       </c>
@@ -723,8 +756,11 @@
         <f t="shared" si="1"/>
         <v>55.498880920239735</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H11">
+        <v>130371</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1">
         <v>33270</v>
       </c>
@@ -748,8 +784,11 @@
         <f t="shared" si="1"/>
         <v>52.91045775388794</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H12">
+        <v>72998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1">
         <v>33298</v>
       </c>
@@ -773,8 +812,11 @@
         <f t="shared" si="1"/>
         <v>52.540265233028286</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H13">
+        <v>136476</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1">
         <v>33329</v>
       </c>
@@ -798,8 +840,11 @@
         <f t="shared" si="1"/>
         <v>52.0604036143651</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H14">
+        <v>191393</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1">
         <v>33359</v>
       </c>
@@ -823,8 +868,11 @@
         <f t="shared" si="1"/>
         <v>49.870229047021979</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H15">
+        <v>164718</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1">
         <v>33390</v>
       </c>
@@ -848,8 +896,11 @@
         <f t="shared" si="1"/>
         <v>48.088108091985561</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H16">
+        <v>108175</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1">
         <v>33420</v>
       </c>
@@ -873,8 +924,11 @@
         <f t="shared" si="1"/>
         <v>45.883960740464651</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H17">
+        <v>143930</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1">
         <v>33451</v>
       </c>
@@ -898,8 +952,11 @@
         <f t="shared" si="1"/>
         <v>46.662845829208564</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H18">
+        <v>129158</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1">
         <v>33482</v>
       </c>
@@ -923,8 +980,11 @@
         <f t="shared" si="1"/>
         <v>43.286601597160605</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H19">
+        <v>90554</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1">
         <v>33512</v>
       </c>
@@ -948,8 +1008,11 @@
         <f t="shared" si="1"/>
         <v>42.361802297107289</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H20">
+        <v>125571</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1">
         <v>33543</v>
       </c>
@@ -973,8 +1036,11 @@
         <f t="shared" si="1"/>
         <v>43.429193960640809</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H21">
+        <v>118833</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1">
         <v>33573</v>
       </c>
@@ -998,8 +1064,11 @@
         <f t="shared" si="1"/>
         <v>44.446108905699944</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H22">
+        <v>157045</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1">
         <v>33604</v>
       </c>
@@ -1023,8 +1092,11 @@
         <f t="shared" si="1"/>
         <v>46.397641138058262</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H23">
+        <v>143585</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1">
         <v>33635</v>
       </c>
@@ -1048,8 +1120,11 @@
         <f t="shared" si="1"/>
         <v>47.841684990163174</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H24">
+        <v>130777</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1">
         <v>33664</v>
       </c>
@@ -1073,8 +1148,11 @@
         <f t="shared" si="1"/>
         <v>45.75612956476651</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H25">
+        <v>172320</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1">
         <v>33695</v>
       </c>
@@ -1098,8 +1176,11 @@
         <f t="shared" si="1"/>
         <v>43.66677424333843</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H26">
+        <v>168503</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="1">
         <v>33725</v>
       </c>
@@ -1123,8 +1204,11 @@
         <f t="shared" si="1"/>
         <v>41.673474786614072</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H27">
+        <v>153874</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="1">
         <v>33756</v>
       </c>
@@ -1148,8 +1232,11 @@
         <f t="shared" si="1"/>
         <v>37.442999226840726</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H28">
+        <v>160366</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="1">
         <v>33786</v>
       </c>
@@ -1173,8 +1260,11 @@
         <f t="shared" si="1"/>
         <v>36.80224196146937</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H29">
+        <v>279455</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1">
         <v>33817</v>
       </c>
@@ -1198,8 +1288,11 @@
         <f t="shared" si="1"/>
         <v>36.031091396239248</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H30">
+        <v>163372</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="1">
         <v>33848</v>
       </c>
@@ -1223,8 +1316,11 @@
         <f t="shared" si="1"/>
         <v>39.033433090130629</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H31">
+        <v>278393</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="1">
         <v>33878</v>
       </c>
@@ -1248,8 +1344,11 @@
         <f t="shared" si="1"/>
         <v>38.720802291708068</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H32">
+        <v>248938</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="1">
         <v>33909</v>
       </c>
@@ -1273,8 +1372,11 @@
         <f t="shared" si="1"/>
         <v>42.363084947402349</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H33">
+        <v>221017</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="1">
         <v>33939</v>
       </c>
@@ -1298,8 +1400,11 @@
         <f t="shared" si="1"/>
         <v>45.304461643523787</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H34">
+        <v>278514</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="1">
         <v>33970</v>
       </c>
@@ -1323,8 +1428,11 @@
         <f t="shared" si="1"/>
         <v>48.622086328078467</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H35">
+        <v>171928</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="1">
         <v>34001</v>
       </c>
@@ -1348,8 +1456,11 @@
         <f t="shared" si="1"/>
         <v>50.858917213402115</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H36">
+        <v>219280</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="1">
         <v>34029</v>
       </c>
@@ -1373,8 +1484,11 @@
         <f t="shared" si="1"/>
         <v>49.609831349425029</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H37">
+        <v>232942</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="1">
         <v>34060</v>
       </c>
@@ -1398,8 +1512,11 @@
         <f t="shared" si="1"/>
         <v>46.994317163914047</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H38">
+        <v>143849</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="1">
         <v>34090</v>
       </c>
@@ -1423,8 +1540,11 @@
         <f t="shared" si="1"/>
         <v>43.646239291742106</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H39">
+        <v>186925</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="1">
         <v>34121</v>
       </c>
@@ -1448,8 +1568,11 @@
         <f t="shared" si="1"/>
         <v>44.533798260955599</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H40">
+        <v>221023</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="1">
         <v>34151</v>
       </c>
@@ -1473,8 +1596,11 @@
         <f t="shared" si="1"/>
         <v>44.755277024744565</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H41">
+        <v>140913</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="1">
         <v>34182</v>
       </c>
@@ -1498,8 +1624,11 @@
         <f t="shared" si="1"/>
         <v>47.599765199629886</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H42">
+        <v>241078</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="1">
         <v>34213</v>
       </c>
@@ -1523,8 +1652,11 @@
         <f t="shared" si="1"/>
         <v>55.277401373928527</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H43">
+        <v>292428</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="1">
         <v>34243</v>
       </c>
@@ -1548,8 +1680,11 @@
         <f t="shared" si="1"/>
         <v>55.421328952983615</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H44">
+        <v>254481</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="1">
         <v>34274</v>
       </c>
@@ -1573,8 +1708,11 @@
         <f t="shared" si="1"/>
         <v>61.179968694835679</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H45">
+        <v>289733</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="1">
         <v>34304</v>
       </c>
@@ -1598,8 +1736,11 @@
         <f t="shared" si="1"/>
         <v>65.803082990044331</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H46">
+        <v>305521</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="1">
         <v>34335</v>
       </c>
@@ -1623,8 +1764,11 @@
         <f t="shared" si="1"/>
         <v>70.407932899679977</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H47">
+        <v>257708</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="1">
         <v>34366</v>
       </c>
@@ -1648,8 +1792,11 @@
         <f t="shared" si="1"/>
         <v>70.001685720690432</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H48">
+        <v>246736</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="1">
         <v>34394</v>
       </c>
@@ -1673,8 +1820,11 @@
         <f t="shared" si="1"/>
         <v>71.373222288509723</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H49">
+        <v>263878</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="1">
         <v>34425</v>
       </c>
@@ -1698,8 +1848,11 @@
         <f t="shared" si="1"/>
         <v>78.970236322991141</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H50">
+        <v>212631</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="1">
         <v>34455</v>
       </c>
@@ -1723,8 +1876,11 @@
         <f t="shared" si="1"/>
         <v>88.671257451355288</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H51">
+        <v>214361.45499999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="1">
         <v>34486</v>
       </c>
@@ -1748,8 +1904,11 @@
         <f t="shared" si="1"/>
         <v>98.735288787208191</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H52">
+        <v>161336</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="1">
         <v>34516</v>
       </c>
@@ -1773,8 +1932,11 @@
         <f t="shared" si="1"/>
         <v>123.50925949502894</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H53">
+        <v>204297</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="1">
         <v>34547</v>
       </c>
@@ -1798,8 +1960,11 @@
         <f t="shared" si="1"/>
         <v>170.91559474393617</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H54">
+        <v>229358</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="1">
         <v>34578</v>
       </c>
@@ -1823,8 +1988,11 @@
         <f t="shared" si="1"/>
         <v>155.35949838197811</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H55">
+        <v>203106</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="1">
         <v>34608</v>
       </c>
@@ -1848,8 +2016,11 @@
         <f t="shared" si="1"/>
         <v>205.34137585119311</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H56">
+        <v>222251</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="1">
         <v>34639</v>
       </c>
@@ -1873,8 +2044,11 @@
         <f t="shared" si="1"/>
         <v>183.92451087886025</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H57">
+        <v>236596</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="1">
         <v>34669</v>
       </c>
@@ -1898,8 +2072,11 @@
         <f t="shared" si="1"/>
         <v>171.61102011215084</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H58">
+        <v>238300</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="1">
         <v>34700</v>
       </c>
@@ -1923,8 +2100,11 @@
         <f t="shared" si="1"/>
         <v>150.24165931299132</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H59">
+        <v>140541</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="1">
         <v>34731</v>
       </c>
@@ -1948,8 +2128,11 @@
         <f t="shared" si="1"/>
         <v>147.37740431956937</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H60">
+        <v>185297</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="1">
         <v>34759</v>
       </c>
@@ -1973,8 +2156,11 @@
         <f t="shared" si="1"/>
         <v>156.14668522707498</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H61">
+        <v>190786</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="1">
         <v>34790</v>
       </c>
@@ -1998,8 +2184,11 @@
         <f t="shared" si="1"/>
         <v>146.3884475774633</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H62">
+        <v>149155</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="1">
         <v>34820</v>
       </c>
@@ -2023,8 +2212,11 @@
         <f t="shared" si="1"/>
         <v>148.5615486036198</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H63">
+        <v>140157</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="1">
         <v>34851</v>
       </c>
@@ -2048,8 +2240,11 @@
         <f t="shared" si="1"/>
         <v>148.57300064591757</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H64">
+        <v>346997</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="1">
         <v>34881</v>
       </c>
@@ -2073,8 +2268,11 @@
         <f t="shared" si="1"/>
         <v>134.05507932446264</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H65">
+        <v>213535</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="1">
         <v>34912</v>
       </c>
@@ -2098,8 +2296,11 @@
         <f t="shared" si="1"/>
         <v>130.17958603439666</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H66">
+        <v>261478</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="1">
         <v>34943</v>
       </c>
@@ -2123,8 +2324,11 @@
         <f t="shared" ref="G67:G130" si="3">E67*1000/D67</f>
         <v>120.40095210465239</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H67">
+        <v>223076</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="1">
         <v>34973</v>
       </c>
@@ -2148,8 +2352,11 @@
         <f t="shared" si="3"/>
         <v>138.40835966298053</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H68">
+        <v>249093</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="1">
         <v>35004</v>
       </c>
@@ -2173,8 +2380,11 @@
         <f t="shared" si="3"/>
         <v>95.52021980690995</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H69">
+        <v>227239.85</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="1">
         <v>35034</v>
       </c>
@@ -2198,8 +2408,11 @@
         <f t="shared" si="3"/>
         <v>139.08417910447761</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H70">
+        <v>287306.15000000002</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="1">
         <v>35065</v>
       </c>
@@ -2223,8 +2436,11 @@
         <f t="shared" si="3"/>
         <v>128.26209132666847</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H71">
+        <v>173749.55</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="1">
         <v>35096</v>
       </c>
@@ -2248,8 +2464,11 @@
         <f t="shared" si="3"/>
         <v>130.77660866046136</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H72">
+        <v>196052.75</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="1">
         <v>35125</v>
       </c>
@@ -2273,8 +2492,11 @@
         <f t="shared" si="3"/>
         <v>171.28758169934642</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H73">
+        <v>224410.65</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="1">
         <v>35156</v>
       </c>
@@ -2298,8 +2520,11 @@
         <f t="shared" si="3"/>
         <v>123.39617224880382</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H74">
+        <v>189377.75</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="1">
         <v>35186</v>
       </c>
@@ -2323,8 +2548,11 @@
         <f t="shared" si="3"/>
         <v>113.09518230064099</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H75">
+        <v>186512.35</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="1">
         <v>35217</v>
       </c>
@@ -2348,8 +2576,11 @@
         <f t="shared" si="3"/>
         <v>104.94624871189708</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H76">
+        <v>249921.05</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="1">
         <v>35247</v>
       </c>
@@ -2373,8 +2604,11 @@
         <f t="shared" si="3"/>
         <v>96.222156329263555</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H77">
+        <v>186380.75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="1">
         <v>35278</v>
       </c>
@@ -2398,8 +2632,11 @@
         <f t="shared" si="3"/>
         <v>89.131853538228057</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H78">
+        <v>230792.75</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="1">
         <v>35309</v>
       </c>
@@ -2423,8 +2660,11 @@
         <f t="shared" si="3"/>
         <v>84.970389568533719</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H79">
+        <v>172447.85</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="1">
         <v>35339</v>
       </c>
@@ -2448,8 +2688,11 @@
         <f t="shared" si="3"/>
         <v>88.466691616766468</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H80">
+        <v>256604.05</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="1">
         <v>35370</v>
       </c>
@@ -2473,8 +2716,11 @@
         <f t="shared" si="3"/>
         <v>86.611626541397527</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H81">
+        <v>217852</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="1">
         <v>35400</v>
       </c>
@@ -2498,8 +2744,11 @@
         <f t="shared" si="3"/>
         <v>83.053874894540201</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H82">
+        <v>234293</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="1">
         <v>35431</v>
       </c>
@@ -2523,8 +2772,11 @@
         <f t="shared" si="3"/>
         <v>84.060898782024353</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H83">
+        <v>182010</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="1">
         <v>35462</v>
       </c>
@@ -2548,8 +2800,11 @@
         <f t="shared" si="3"/>
         <v>111.27964189264178</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H84">
+        <v>164401</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="1">
         <v>35490</v>
       </c>
@@ -2573,8 +2828,11 @@
         <f t="shared" si="3"/>
         <v>108.60286941245364</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H85">
+        <v>188865</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="1">
         <v>35521</v>
       </c>
@@ -2598,8 +2856,11 @@
         <f t="shared" si="3"/>
         <v>99.53784514877762</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H86">
+        <v>143030.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="1">
         <v>35551</v>
       </c>
@@ -2623,8 +2884,11 @@
         <f t="shared" si="3"/>
         <v>101.64404203114999</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H87">
+        <v>143851</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="1">
         <v>35582</v>
       </c>
@@ -2648,8 +2912,11 @@
         <f t="shared" si="3"/>
         <v>108.80273104120946</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H88">
+        <v>168810</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="1">
         <v>35612</v>
       </c>
@@ -2673,8 +2940,11 @@
         <f t="shared" si="3"/>
         <v>107.04973157925787</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H89">
+        <v>259333</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="1">
         <v>35643</v>
       </c>
@@ -2698,8 +2968,11 @@
         <f t="shared" si="3"/>
         <v>95.028425865006668</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H90">
+        <v>240014</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="1">
         <v>35674</v>
       </c>
@@ -2723,8 +2996,11 @@
         <f t="shared" si="3"/>
         <v>96.977124183006538</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H91">
+        <v>240374</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="1">
         <v>35704</v>
       </c>
@@ -2748,8 +3024,11 @@
         <f t="shared" si="3"/>
         <v>102.25542712151113</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H92">
+        <v>224882</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="1">
         <v>35735</v>
       </c>
@@ -2773,8 +3052,11 @@
         <f t="shared" si="3"/>
         <v>116.49773697966469</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H93">
+        <v>135160.70000000001</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="1">
         <v>35765</v>
       </c>
@@ -2798,8 +3080,11 @@
         <f t="shared" si="3"/>
         <v>116.31608868675384</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H94">
+        <v>243142.3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="1">
         <v>35796</v>
       </c>
@@ -2823,8 +3108,11 @@
         <f t="shared" si="3"/>
         <v>126.09970674486803</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H95">
+        <v>139372.29999999999</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="1">
         <v>35827</v>
       </c>
@@ -2848,8 +3136,11 @@
         <f t="shared" si="3"/>
         <v>142.01680672268907</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H96">
+        <v>135891.29999999999</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="1">
         <v>35855</v>
       </c>
@@ -2873,8 +3164,11 @@
         <f t="shared" si="3"/>
         <v>130.20036429872496</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H97">
+        <v>116877</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="1">
         <v>35886</v>
       </c>
@@ -2898,8 +3192,11 @@
         <f t="shared" si="3"/>
         <v>132.79656468062265</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H98">
+        <v>116371</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="1">
         <v>35916</v>
       </c>
@@ -2923,8 +3220,11 @@
         <f t="shared" si="3"/>
         <v>109.90094190376519</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H99">
+        <v>148613</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="1">
         <v>35947</v>
       </c>
@@ -2948,8 +3248,11 @@
         <f t="shared" si="3"/>
         <v>106.17459989868478</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H100">
+        <v>146998</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="1">
         <v>35977</v>
       </c>
@@ -2973,8 +3276,11 @@
         <f t="shared" si="3"/>
         <v>99.996073658172676</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H101">
+        <v>191957.8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="1">
         <v>36008</v>
       </c>
@@ -2998,8 +3304,11 @@
         <f t="shared" si="3"/>
         <v>97.956440123613646</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H102">
+        <v>145771.29999999999</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="1">
         <v>36039</v>
       </c>
@@ -3023,8 +3332,11 @@
         <f t="shared" si="3"/>
         <v>95.879155002245298</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H103">
+        <v>123624.2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="1">
         <v>36069</v>
       </c>
@@ -3048,8 +3360,11 @@
         <f t="shared" si="3"/>
         <v>94.605824983044698</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H104">
+        <v>109284.5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="1">
         <v>36100</v>
       </c>
@@ -3073,8 +3388,11 @@
         <f t="shared" si="3"/>
         <v>95.165735567970202</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H105">
+        <v>166037.79999999999</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="1">
         <v>36130</v>
       </c>
@@ -3098,8 +3416,11 @@
         <f t="shared" si="3"/>
         <v>102.17355371900827</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H106">
+        <v>121037.8</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="1">
         <v>36161</v>
       </c>
@@ -3123,8 +3444,11 @@
         <f t="shared" si="3"/>
         <v>100.70589543113351</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H107">
+        <v>136498.20000000001</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="1">
         <v>36192</v>
       </c>
@@ -3148,8 +3472,11 @@
         <f t="shared" si="3"/>
         <v>101.82003691088872</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H108">
+        <v>162608.5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="1">
         <v>36220</v>
       </c>
@@ -3173,8 +3500,11 @@
         <f t="shared" si="3"/>
         <v>91.928060992437622</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H109">
+        <v>190073.8</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="1">
         <v>36251</v>
       </c>
@@ -3198,8 +3528,11 @@
         <f t="shared" si="3"/>
         <v>87.519188890078894</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H110">
+        <v>133497.29999999999</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="1">
         <v>36281</v>
       </c>
@@ -3223,8 +3556,11 @@
         <f t="shared" si="3"/>
         <v>81.293776668545206</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H111">
+        <v>109270.8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="1">
         <v>36312</v>
       </c>
@@ -3248,8 +3584,11 @@
         <f t="shared" si="3"/>
         <v>81.268601543098711</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H112">
+        <v>124346</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="1">
         <v>36342</v>
       </c>
@@ -3273,8 +3612,11 @@
         <f t="shared" si="3"/>
         <v>74.023126324261284</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H113">
+        <v>140144</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="1">
         <v>36373</v>
       </c>
@@ -3298,8 +3640,11 @@
         <f t="shared" si="3"/>
         <v>73.046656776165122</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H114">
+        <v>168928</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="1">
         <v>36404</v>
       </c>
@@ -3323,8 +3668,11 @@
         <f t="shared" si="3"/>
         <v>72.630891468364467</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H115">
+        <v>223520</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="1">
         <v>36434</v>
       </c>
@@ -3348,8 +3696,11 @@
         <f t="shared" si="3"/>
         <v>71.462741490340392</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H116">
+        <v>196686</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="1">
         <v>36465</v>
       </c>
@@ -3373,8 +3724,11 @@
         <f t="shared" si="3"/>
         <v>75.426102557530712</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H117">
+        <v>172237</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="1">
         <v>36495</v>
       </c>
@@ -3398,8 +3752,11 @@
         <f t="shared" si="3"/>
         <v>79.825137791028382</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H118">
+        <v>202881</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="1">
         <v>36526</v>
       </c>
@@ -3423,8 +3780,11 @@
         <f t="shared" si="3"/>
         <v>74.565981414627615</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H119">
+        <v>105184</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="1">
         <v>36557</v>
       </c>
@@ -3448,8 +3808,11 @@
         <f t="shared" si="3"/>
         <v>75.710017251755261</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H120">
+        <v>153575</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="1">
         <v>36586</v>
       </c>
@@ -3473,8 +3836,11 @@
         <f t="shared" si="3"/>
         <v>69.976656958158699</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H121">
+        <v>117774</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="1">
         <v>36617</v>
       </c>
@@ -3498,8 +3864,11 @@
         <f t="shared" si="3"/>
         <v>73.609449575450611</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H122">
+        <v>159797</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="1">
         <v>36647</v>
       </c>
@@ -3523,8 +3892,11 @@
         <f t="shared" si="3"/>
         <v>56.183876401174139</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H123">
+        <v>162003</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="1">
         <v>36678</v>
       </c>
@@ -3548,8 +3920,11 @@
         <f t="shared" si="3"/>
         <v>55.705172332361194</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H124">
+        <v>208461</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="1">
         <v>36708</v>
       </c>
@@ -3573,8 +3948,11 @@
         <f t="shared" si="3"/>
         <v>54.525928002691487</v>
       </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H125">
+        <v>157379</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="1">
         <v>36739</v>
       </c>
@@ -3598,8 +3976,11 @@
         <f t="shared" si="3"/>
         <v>58.859598360435179</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H126">
+        <v>176319</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="1">
         <v>36770</v>
       </c>
@@ -3623,8 +4004,11 @@
         <f t="shared" si="3"/>
         <v>60.307570727718719</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H127">
+        <v>194723</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="1">
         <v>36800</v>
       </c>
@@ -3648,8 +4032,11 @@
         <f t="shared" si="3"/>
         <v>56.948037185318711</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H128">
+        <v>220776</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="1">
         <v>36831</v>
       </c>
@@ -3673,8 +4060,11 @@
         <f t="shared" si="3"/>
         <v>55.440819441654959</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H129">
+        <v>143057</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="1">
         <v>36861</v>
       </c>
@@ -3698,8 +4088,11 @@
         <f t="shared" si="3"/>
         <v>50.179918671135646</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H130">
+        <v>267168</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="1">
         <v>36892</v>
       </c>
@@ -3723,8 +4116,11 @@
         <f t="shared" ref="G131:G194" si="5">E131*1000/D131</f>
         <v>48.016450879156586</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H131">
+        <v>187789</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="1">
         <v>36923</v>
       </c>
@@ -3748,8 +4144,11 @@
         <f t="shared" si="5"/>
         <v>53.834275027852939</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H132">
+        <v>173543</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="1">
         <v>36951</v>
       </c>
@@ -3773,8 +4172,11 @@
         <f t="shared" si="5"/>
         <v>47.09261590470058</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H133">
+        <v>196722</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="1">
         <v>36982</v>
       </c>
@@ -3798,8 +4200,11 @@
         <f t="shared" si="5"/>
         <v>42.493384046946318</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H134">
+        <v>217120</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="1">
         <v>37012</v>
       </c>
@@ -3823,8 +4228,11 @@
         <f t="shared" si="5"/>
         <v>34.9569844503648</v>
       </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H135">
+        <v>213733</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="1">
         <v>37043</v>
       </c>
@@ -3848,8 +4256,11 @@
         <f t="shared" si="5"/>
         <v>32.729808887624124</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H136">
+        <v>216312</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="1">
         <v>37073</v>
       </c>
@@ -3873,8 +4284,11 @@
         <f t="shared" si="5"/>
         <v>30.816625707005908</v>
       </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H137">
+        <v>201305</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="1">
         <v>37104</v>
       </c>
@@ -3898,8 +4312,11 @@
         <f t="shared" si="5"/>
         <v>27.43426888880029</v>
       </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H138">
+        <v>196252</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="1">
         <v>37135</v>
       </c>
@@ -3923,8 +4340,11 @@
         <f t="shared" si="5"/>
         <v>26.509335330959104</v>
       </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H139">
+        <v>239590</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="1">
         <v>37165</v>
       </c>
@@ -3948,8 +4368,11 @@
         <f t="shared" si="5"/>
         <v>24.281708818716481</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H140">
+        <v>216015.28</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="1">
         <v>37196</v>
       </c>
@@ -3973,8 +4396,11 @@
         <f t="shared" si="5"/>
         <v>27.899357900491147</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H141">
+        <v>208057</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="1">
         <v>37226</v>
       </c>
@@ -3998,8 +4424,11 @@
         <f t="shared" si="5"/>
         <v>25.11244608695652</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H142">
+        <v>227453.11333333334</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="1">
         <v>37257</v>
       </c>
@@ -4023,8 +4452,11 @@
         <f t="shared" si="5"/>
         <v>24.01253843737295</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H143">
+        <v>163620</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="1">
         <v>37288</v>
       </c>
@@ -4048,8 +4480,11 @@
         <f t="shared" si="5"/>
         <v>26.251529331633925</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H144">
+        <v>180828.6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" s="1">
         <v>37316</v>
       </c>
@@ -4073,8 +4508,11 @@
         <f t="shared" si="5"/>
         <v>25.079832823886413</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H145">
+        <v>240660</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="1">
         <v>37347</v>
       </c>
@@ -4098,8 +4536,11 @@
         <f t="shared" si="5"/>
         <v>27.256839148312501</v>
       </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H146">
+        <v>176692.3</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="1">
         <v>37377</v>
       </c>
@@ -4123,8 +4564,11 @@
         <f t="shared" si="5"/>
         <v>27.349910728598644</v>
       </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H147">
+        <v>207982.1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="1">
         <v>37408</v>
       </c>
@@ -4148,8 +4592,11 @@
         <f t="shared" si="5"/>
         <v>28.17764890288559</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H148">
+        <v>216504.1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="1">
         <v>37438</v>
       </c>
@@ -4173,8 +4620,11 @@
         <f t="shared" si="5"/>
         <v>28.479328741724292</v>
       </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H149">
+        <v>178920.6</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="1">
         <v>37469</v>
       </c>
@@ -4198,8 +4648,11 @@
         <f t="shared" si="5"/>
         <v>27.903828154337656</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H150">
+        <v>222507.45876666668</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="1">
         <v>37500</v>
       </c>
@@ -4223,8 +4676,11 @@
         <f t="shared" si="5"/>
         <v>28.734947369838846</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H151">
+        <v>217379.78340000001</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="1">
         <v>37530</v>
       </c>
@@ -4248,8 +4704,11 @@
         <f t="shared" si="5"/>
         <v>31.712210637042453</v>
       </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H152">
+        <v>218098.22146666667</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="1">
         <v>37561</v>
       </c>
@@ -4273,8 +4732,11 @@
         <f t="shared" si="5"/>
         <v>34.435967646093424</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H153">
+        <v>230358.2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="1">
         <v>37591</v>
       </c>
@@ -4298,8 +4760,11 @@
         <f t="shared" si="5"/>
         <v>37.90947333447204</v>
       </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H154">
+        <v>292985.2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="1">
         <v>37622</v>
       </c>
@@ -4323,8 +4788,11 @@
         <f t="shared" si="5"/>
         <v>40.615659390052464</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H155">
+        <v>182558.95666666667</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="1">
         <v>37653</v>
       </c>
@@ -4348,8 +4816,11 @@
         <f t="shared" si="5"/>
         <v>44.257244778964228</v>
       </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H156">
+        <v>246568.74666666667</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="1">
         <v>37681</v>
       </c>
@@ -4373,8 +4844,11 @@
         <f t="shared" si="5"/>
         <v>43.573432501382619</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H157">
+        <v>235032.72</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="1">
         <v>37712</v>
       </c>
@@ -4398,8 +4872,11 @@
         <f t="shared" si="5"/>
         <v>40.896730925641428</v>
       </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H158">
+        <v>201323.33</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" s="1">
         <v>37742</v>
       </c>
@@ -4423,8 +4900,11 @@
         <f t="shared" si="5"/>
         <v>41.135291334082133</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H159">
+        <v>237484.30333333334</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" s="1">
         <v>37773</v>
       </c>
@@ -4448,8 +4928,11 @@
         <f t="shared" si="5"/>
         <v>39.133152377386743</v>
       </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H160">
+        <v>248940.9</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" s="1">
         <v>37803</v>
       </c>
@@ -4473,8 +4956,11 @@
         <f t="shared" si="5"/>
         <v>38.911052786788559</v>
       </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H161">
+        <v>250195.01</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" s="1">
         <v>37834</v>
       </c>
@@ -4498,8 +4984,11 @@
         <f t="shared" si="5"/>
         <v>40.308417345485978</v>
       </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H162">
+        <v>210483</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" s="1">
         <v>37865</v>
       </c>
@@ -4523,8 +5012,11 @@
         <f t="shared" si="5"/>
         <v>44.251494782831202</v>
       </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H163">
+        <v>236065.74333333332</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" s="1">
         <v>37895</v>
       </c>
@@ -4548,8 +5040,11 @@
         <f t="shared" si="5"/>
         <v>44.911259908123377</v>
       </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H164">
+        <v>234847.47</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" s="1">
         <v>37926</v>
       </c>
@@ -4573,8 +5068,11 @@
         <f t="shared" si="5"/>
         <v>46.815142912711991</v>
       </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H165">
+        <v>295867.13</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" s="1">
         <v>37956</v>
       </c>
@@ -4598,8 +5096,11 @@
         <f t="shared" si="5"/>
         <v>47.34046046903719</v>
       </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H166">
+        <v>268258.20666666667</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" s="1">
         <v>37987</v>
       </c>
@@ -4623,8 +5124,11 @@
         <f t="shared" si="5"/>
         <v>49.839117805271655</v>
       </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H167">
+        <v>199353.51826000007</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" s="1">
         <v>38018</v>
       </c>
@@ -4648,8 +5152,11 @@
         <f t="shared" si="5"/>
         <v>51.81612095815165</v>
       </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H168">
+        <v>157352.82697333334</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" s="1">
         <v>38047</v>
       </c>
@@ -4673,8 +5180,11 @@
         <f t="shared" si="5"/>
         <v>52.622224207153117</v>
       </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H169">
+        <v>306523.74605666666</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" s="1">
         <v>38078</v>
       </c>
@@ -4698,8 +5208,11 @@
         <f t="shared" si="5"/>
         <v>50.146124608401003</v>
       </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H170">
+        <v>287338.93799000006</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" s="1">
         <v>38108</v>
       </c>
@@ -4723,8 +5236,11 @@
         <f t="shared" si="5"/>
         <v>50.517251321741973</v>
       </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H171">
+        <v>307582.54375333333</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" s="1">
         <v>38139</v>
       </c>
@@ -4748,8 +5264,11 @@
         <f t="shared" si="5"/>
         <v>49.020353815902666</v>
       </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H172">
+        <v>279670.52832333336</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" s="1">
         <v>38169</v>
       </c>
@@ -4773,8 +5292,11 @@
         <f t="shared" si="5"/>
         <v>48.006017850839598</v>
       </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H173">
+        <v>306139.21658666676</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" s="1">
         <v>38200</v>
       </c>
@@ -4798,8 +5320,11 @@
         <f t="shared" si="5"/>
         <v>43.711856243314699</v>
       </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H174">
+        <v>302506.98274333333</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" s="1">
         <v>38231</v>
       </c>
@@ -4823,8 +5348,11 @@
         <f t="shared" si="5"/>
         <v>46.516162330852723</v>
       </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H175">
+        <v>244056.51707666667</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" s="1">
         <v>38261</v>
       </c>
@@ -4848,8 +5376,11 @@
         <f t="shared" si="5"/>
         <v>49.091481807399475</v>
       </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H176">
+        <v>224103.87029333331</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" s="1">
         <v>38292</v>
       </c>
@@ -4873,8 +5404,11 @@
         <f t="shared" si="5"/>
         <v>50.892157403691819</v>
       </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H177">
+        <v>249550.84634999998</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" s="1">
         <v>38322</v>
       </c>
@@ -4898,8 +5432,11 @@
         <f t="shared" si="5"/>
         <v>51.412529003912958</v>
       </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H178">
+        <v>319777.24939333339</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" s="1">
         <v>38353</v>
       </c>
@@ -4923,8 +5460,11 @@
         <f t="shared" si="5"/>
         <v>52.775354893410857</v>
       </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H179">
+        <v>264733.75786000001</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" s="1">
         <v>38384</v>
       </c>
@@ -4948,8 +5488,11 @@
         <f t="shared" si="5"/>
         <v>56.080693231097982</v>
       </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H180">
+        <v>248242.99153333329</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" s="1">
         <v>38412</v>
       </c>
@@ -4973,8 +5516,11 @@
         <f t="shared" si="5"/>
         <v>58.783082748469397</v>
       </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H181">
+        <v>315360.67064666672</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" s="1">
         <v>38443</v>
       </c>
@@ -4998,8 +5544,11 @@
         <f t="shared" si="5"/>
         <v>60.832391858095583</v>
       </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H182">
+        <v>265275.09350333334</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" s="1">
         <v>38473</v>
       </c>
@@ -5023,8 +5572,11 @@
         <f t="shared" si="5"/>
         <v>63.442327179849244</v>
       </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H183">
+        <v>362515.18155666668</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A184" s="1">
         <v>38504</v>
       </c>
@@ -5048,8 +5600,11 @@
         <f t="shared" si="5"/>
         <v>67.685022522522516</v>
       </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H184">
+        <v>265889.60168333334</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" s="1">
         <v>38534</v>
       </c>
@@ -5073,8 +5628,11 @@
         <f t="shared" si="5"/>
         <v>71.640743219991421</v>
       </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H185">
+        <v>333089.65672666661</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A186" s="1">
         <v>38565</v>
       </c>
@@ -5098,8 +5656,11 @@
         <f t="shared" si="5"/>
         <v>69.648203302553995</v>
       </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H186">
+        <v>278566.61360666668</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" s="1">
         <v>38596</v>
       </c>
@@ -5123,8 +5684,11 @@
         <f t="shared" si="5"/>
         <v>66.546798789442107</v>
       </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H187">
+        <v>260105.52186666668</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" s="1">
         <v>38626</v>
       </c>
@@ -5148,8 +5712,11 @@
         <f t="shared" si="5"/>
         <v>68.023209697627024</v>
       </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H188">
+        <v>273364.86970000004</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A189" s="1">
         <v>38657</v>
       </c>
@@ -5173,8 +5740,11 @@
         <f t="shared" si="5"/>
         <v>71.675509993037636</v>
       </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H189">
+        <v>291044.81856666668</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A190" s="1">
         <v>38687</v>
       </c>
@@ -5198,8 +5768,11 @@
         <f t="shared" si="5"/>
         <v>68.711876830584245</v>
       </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H190">
+        <v>366979.22902333335</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A191" s="1">
         <v>38718</v>
       </c>
@@ -5223,8 +5796,11 @@
         <f t="shared" si="5"/>
         <v>71.11789209261687</v>
       </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H191">
+        <v>166880.37504666677</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A192" s="1">
         <v>38749</v>
       </c>
@@ -5248,8 +5824,11 @@
         <f t="shared" si="5"/>
         <v>81.438660757195493</v>
       </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H192">
+        <v>193094.42810666678</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A193" s="1">
         <v>38777</v>
       </c>
@@ -5273,8 +5852,11 @@
         <f t="shared" si="5"/>
         <v>85.020375792945941</v>
       </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H193">
+        <v>242198.46221999961</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A194" s="1">
         <v>38808</v>
       </c>
@@ -5298,8 +5880,11 @@
         <f t="shared" si="5"/>
         <v>94.294531787363653</v>
       </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H194">
+        <v>253377</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A195" s="1">
         <v>38838</v>
       </c>
@@ -5323,8 +5908,11 @@
         <f t="shared" ref="G195:G258" si="7">E195*1000/D195</f>
         <v>79.209020074141421</v>
       </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H195">
+        <v>284073</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A196" s="1">
         <v>38869</v>
       </c>
@@ -5348,8 +5936,11 @@
         <f t="shared" si="7"/>
         <v>75.608786411557986</v>
       </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H196">
+        <v>250097</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A197" s="1">
         <v>38899</v>
       </c>
@@ -5373,8 +5964,11 @@
         <f t="shared" si="7"/>
         <v>75.580766044258951</v>
       </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H197">
+        <v>244466</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A198" s="1">
         <v>38930</v>
       </c>
@@ -5398,8 +5992,11 @@
         <f t="shared" si="7"/>
         <v>79.895544402329861</v>
       </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H198">
+        <v>308892</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A199" s="1">
         <v>38961</v>
       </c>
@@ -5423,8 +6020,11 @@
         <f t="shared" si="7"/>
         <v>81.286945453601831</v>
       </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H199">
+        <v>191754</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A200" s="1">
         <v>38991</v>
       </c>
@@ -5448,8 +6048,11 @@
         <f t="shared" si="7"/>
         <v>87.750099061112522</v>
       </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H200">
+        <v>222967</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A201" s="1">
         <v>39022</v>
       </c>
@@ -5473,8 +6076,11 @@
         <f t="shared" si="7"/>
         <v>90.69826823820047</v>
       </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H201">
+        <v>265252</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A202" s="1">
         <v>39052</v>
       </c>
@@ -5498,8 +6104,11 @@
         <f t="shared" si="7"/>
         <v>97.411548148148157</v>
       </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H202">
+        <v>340613</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A203" s="1">
         <v>39083</v>
       </c>
@@ -5523,8 +6132,11 @@
         <f t="shared" si="7"/>
         <v>95.77226679774644</v>
       </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H203">
+        <v>256636</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A204" s="1">
         <v>39114</v>
       </c>
@@ -5548,8 +6160,11 @@
         <f t="shared" si="7"/>
         <v>108.0193226305403</v>
       </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H204">
+        <v>228945</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A205" s="1">
         <v>39142</v>
       </c>
@@ -5573,8 +6188,11 @@
         <f t="shared" si="7"/>
         <v>114.35420486302542</v>
       </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H205">
+        <v>262164</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A206" s="1">
         <v>39173</v>
       </c>
@@ -5598,8 +6216,11 @@
         <f t="shared" si="7"/>
         <v>107.99596232450683</v>
       </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H206">
+        <v>245983</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A207" s="1">
         <v>39203</v>
       </c>
@@ -5623,8 +6244,11 @@
         <f t="shared" si="7"/>
         <v>98.382623316243681</v>
       </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H207">
+        <v>307639</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A208" s="1">
         <v>39234</v>
       </c>
@@ -5648,8 +6272,11 @@
         <f t="shared" si="7"/>
         <v>99.284155323920615</v>
       </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H208">
+        <v>289320</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A209" s="1">
         <v>39264</v>
       </c>
@@ -5673,8 +6300,11 @@
         <f t="shared" si="7"/>
         <v>107.94407374617151</v>
       </c>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H209">
+        <v>323176</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A210" s="1">
         <v>39295</v>
       </c>
@@ -5698,8 +6328,11 @@
         <f t="shared" si="7"/>
         <v>109.92585487944629</v>
       </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H210">
+        <v>286266</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A211" s="1">
         <v>39326</v>
       </c>
@@ -5723,8 +6356,11 @@
         <f t="shared" si="7"/>
         <v>108.66962044248525</v>
       </c>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H211">
+        <v>297962</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A212" s="1">
         <v>39356</v>
       </c>
@@ -5748,8 +6384,11 @@
         <f t="shared" si="7"/>
         <v>117.42238368568694</v>
       </c>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H212">
+        <v>294699</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A213" s="1">
         <v>39387</v>
       </c>
@@ -5773,8 +6412,11 @@
         <f t="shared" si="7"/>
         <v>118.73461006340433</v>
       </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H213">
+        <v>299268</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A214" s="1">
         <v>39417</v>
       </c>
@@ -5798,8 +6440,11 @@
         <f t="shared" si="7"/>
         <v>120.95100729639124</v>
       </c>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H214">
+        <v>281619</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A215" s="1">
         <v>39448</v>
       </c>
@@ -5823,8 +6468,11 @@
         <f t="shared" si="7"/>
         <v>126.52328557375647</v>
       </c>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H215">
+        <v>322661</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A216" s="1">
         <v>39479</v>
       </c>
@@ -5848,8 +6496,11 @@
         <f t="shared" si="7"/>
         <v>128.92236103970296</v>
       </c>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H216">
+        <v>271012</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A217" s="1">
         <v>39508</v>
       </c>
@@ -5873,8 +6524,11 @@
         <f t="shared" si="7"/>
         <v>143.53572460167194</v>
       </c>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H217">
+        <v>307917</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A218" s="1">
         <v>39539</v>
       </c>
@@ -5898,8 +6552,11 @@
         <f t="shared" si="7"/>
         <v>141.88518712233929</v>
       </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H218">
+        <v>302774</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A219" s="1">
         <v>39569</v>
       </c>
@@ -5923,8 +6580,11 @@
         <f t="shared" si="7"/>
         <v>135.14970142807783</v>
       </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H219">
+        <v>290568</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A220" s="1">
         <v>39600</v>
       </c>
@@ -5948,8 +6608,11 @@
         <f t="shared" si="7"/>
         <v>134.30310398643161</v>
       </c>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H220">
+        <v>260125</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A221" s="1">
         <v>39630</v>
       </c>
@@ -5973,8 +6636,11 @@
         <f t="shared" si="7"/>
         <v>134.12133749082125</v>
       </c>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H221">
+        <v>296119</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A222" s="1">
         <v>39661</v>
       </c>
@@ -5998,8 +6664,11 @@
         <f t="shared" si="7"/>
         <v>137.44785867101044</v>
       </c>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H222">
+        <v>297617</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A223" s="1">
         <v>39692</v>
       </c>
@@ -6023,8 +6692,11 @@
         <f t="shared" si="7"/>
         <v>137.72593680833094</v>
       </c>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H223">
+        <v>284332</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A224" s="1">
         <v>39722</v>
       </c>
@@ -6048,8 +6720,11 @@
         <f t="shared" si="7"/>
         <v>126.34179954200629</v>
       </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H224">
+        <v>262765</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A225" s="1">
         <v>39753</v>
       </c>
@@ -6073,8 +6748,11 @@
         <f t="shared" si="7"/>
         <v>114.99945464246601</v>
       </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H225">
+        <v>218455</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A226" s="1">
         <v>39783</v>
       </c>
@@ -6098,8 +6776,11 @@
         <f t="shared" si="7"/>
         <v>113.21432311692354</v>
       </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H226">
+        <v>250586</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A227" s="1">
         <v>39814</v>
       </c>
@@ -6123,8 +6804,11 @@
         <f t="shared" si="7"/>
         <v>116.66976346577087</v>
       </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H227">
+        <v>213974</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A228" s="1">
         <v>39845</v>
       </c>
@@ -6148,8 +6832,11 @@
         <f t="shared" si="7"/>
         <v>108.99183831325301</v>
       </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H228">
+        <v>224445</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A229" s="1">
         <v>39873</v>
       </c>
@@ -6173,8 +6860,11 @@
         <f t="shared" si="7"/>
         <v>103.25224183120741</v>
       </c>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H229">
+        <v>250185</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A230" s="1">
         <v>39904</v>
       </c>
@@ -6198,8 +6888,11 @@
         <f t="shared" si="7"/>
         <v>99.386568170408083</v>
       </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H230">
+        <v>252183</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A231" s="1">
         <v>39934</v>
       </c>
@@ -6223,8 +6916,11 @@
         <f t="shared" si="7"/>
         <v>95.266596244639842</v>
       </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H231">
+        <v>234246</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A232" s="1">
         <v>39965</v>
       </c>
@@ -6248,8 +6944,11 @@
         <f t="shared" si="7"/>
         <v>94.812854983570645</v>
       </c>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H232">
+        <v>224003</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A233" s="1">
         <v>39995</v>
       </c>
@@ -6273,8 +6972,11 @@
         <f t="shared" si="7"/>
         <v>90.166959269255329</v>
       </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H233">
+        <v>258079</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A234" s="1">
         <v>40026</v>
       </c>
@@ -6298,8 +7000,11 @@
         <f t="shared" si="7"/>
         <v>91.726068210258191</v>
       </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H234">
+        <v>213960</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A235" s="1">
         <v>40057</v>
       </c>
@@ -6323,8 +7028,11 @@
         <f t="shared" si="7"/>
         <v>97.417311589469364</v>
       </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H235">
+        <v>262386</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A236" s="1">
         <v>40087</v>
       </c>
@@ -6348,8 +7056,11 @@
         <f t="shared" si="7"/>
         <v>93.331810128991634</v>
       </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H236">
+        <v>263777</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A237" s="1">
         <v>40118</v>
       </c>
@@ -6373,8 +7084,11 @@
         <f t="shared" si="7"/>
         <v>95.620856444974407</v>
       </c>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H237">
+        <v>238751</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A238" s="1">
         <v>40148</v>
       </c>
@@ -6398,8 +7112,11 @@
         <f t="shared" si="7"/>
         <v>94.826635376289502</v>
       </c>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H238">
+        <v>276109</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A239" s="1">
         <v>40179</v>
       </c>
@@ -6423,8 +7140,11 @@
         <f t="shared" si="7"/>
         <v>102.20831361954276</v>
       </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H239">
+        <v>240759</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A240" s="1">
         <v>40210</v>
       </c>
@@ -6448,8 +7168,11 @@
         <f t="shared" si="7"/>
         <v>107.59186794632542</v>
       </c>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H240">
+        <v>237582</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A241" s="1">
         <v>40238</v>
       </c>
@@ -6473,8 +7196,11 @@
         <f t="shared" si="7"/>
         <v>108.23411941796287</v>
       </c>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H241">
+        <v>264587</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A242" s="1">
         <v>40269</v>
       </c>
@@ -6498,8 +7224,11 @@
         <f t="shared" si="7"/>
         <v>105.27710829140233</v>
       </c>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H242">
+        <v>300129</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A243" s="1">
         <v>40299</v>
       </c>
@@ -6523,8 +7252,11 @@
         <f t="shared" si="7"/>
         <v>90.701584037015621</v>
       </c>
-    </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H243">
+        <v>313399</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A244" s="1">
         <v>40330</v>
       </c>
@@ -6548,8 +7280,11 @@
         <f t="shared" si="7"/>
         <v>90.770514833942997</v>
       </c>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H244">
+        <v>316192</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A245" s="1">
         <v>40360</v>
       </c>
@@ -6573,8 +7308,11 @@
         <f t="shared" si="7"/>
         <v>99.548547084367243</v>
       </c>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H245">
+        <v>276839</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A246" s="1">
         <v>40391</v>
       </c>
@@ -6598,8 +7336,11 @@
         <f t="shared" si="7"/>
         <v>104.75096318211703</v>
       </c>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H246">
+        <v>215240</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A247" s="1">
         <v>40422</v>
       </c>
@@ -6623,8 +7364,11 @@
         <f t="shared" si="7"/>
         <v>104.08245160098836</v>
       </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H247">
+        <v>297647</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A248" s="1">
         <v>40452</v>
       </c>
@@ -6648,8 +7392,11 @@
         <f t="shared" si="7"/>
         <v>108.26978087458788</v>
       </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H248">
+        <v>308130</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A249" s="1">
         <v>40483</v>
       </c>
@@ -6673,8 +7420,11 @@
         <f t="shared" si="7"/>
         <v>107.94370645167976</v>
       </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H249">
+        <v>270248</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A250" s="1">
         <v>40513</v>
       </c>
@@ -6698,8 +7448,11 @@
         <f t="shared" si="7"/>
         <v>109.67919293346937</v>
       </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H250">
+        <v>321378</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A251" s="1">
         <v>40544</v>
       </c>
@@ -6723,8 +7476,11 @@
         <f t="shared" si="7"/>
         <v>115.00126865557876</v>
       </c>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H251">
+        <v>203324</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A252" s="1">
         <v>40575</v>
       </c>
@@ -6748,8 +7504,11 @@
         <f t="shared" si="7"/>
         <v>123.80633734395299</v>
       </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H252">
+        <v>264862</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A253" s="1">
         <v>40603</v>
       </c>
@@ -6773,8 +7532,11 @@
         <f t="shared" si="7"/>
         <v>136.7767875482059</v>
       </c>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H253">
+        <v>363399</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A254" s="1">
         <v>40634</v>
       </c>
@@ -6798,8 +7560,11 @@
         <f t="shared" si="7"/>
         <v>142.66442004927302</v>
       </c>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H254">
+        <v>305656</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A255" s="1">
         <v>40664</v>
       </c>
@@ -6823,8 +7588,11 @@
         <f t="shared" si="7"/>
         <v>142.84801253038663</v>
       </c>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H255">
+        <v>260768</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A256" s="1">
         <v>40695</v>
       </c>
@@ -6848,8 +7616,11 @@
         <f t="shared" si="7"/>
         <v>142.19954851900039</v>
       </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H256">
+        <v>305900</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A257" s="1">
         <v>40725</v>
       </c>
@@ -6873,8 +7644,11 @@
         <f t="shared" si="7"/>
         <v>144.61106497230418</v>
       </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H257">
+        <v>291460</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A258" s="1">
         <v>40756</v>
       </c>
@@ -6898,8 +7672,11 @@
         <f t="shared" si="7"/>
         <v>140.97521506010264</v>
       </c>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H258">
+        <v>315122</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A259" s="1">
         <v>40787</v>
       </c>
@@ -6923,8 +7700,11 @@
         <f t="shared" ref="G259:G322" si="9">E259*1000/D259</f>
         <v>142.55947657757764</v>
       </c>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H259">
+        <v>327383</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A260" s="1">
         <v>40817</v>
       </c>
@@ -6948,8 +7728,11 @@
         <f t="shared" si="9"/>
         <v>137.61087546578591</v>
       </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H260">
+        <v>251949</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A261" s="1">
         <v>40848</v>
       </c>
@@ -6973,8 +7756,11 @@
         <f t="shared" si="9"/>
         <v>133.13706905452921</v>
       </c>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H261">
+        <v>293753</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A262" s="1">
         <v>40878</v>
       </c>
@@ -6998,8 +7784,11 @@
         <f t="shared" si="9"/>
         <v>127.21148595487139</v>
       </c>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H262">
+        <v>415857</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A263" s="1">
         <v>40909</v>
       </c>
@@ -7023,8 +7812,11 @@
         <f t="shared" si="9"/>
         <v>125.76935380421712</v>
       </c>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H263">
+        <v>207169</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A264" s="1">
         <v>40940</v>
       </c>
@@ -7048,8 +7840,11 @@
         <f t="shared" si="9"/>
         <v>138.15614556830818</v>
       </c>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H264">
+        <v>254651</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A265" s="1">
         <v>40969</v>
       </c>
@@ -7073,8 +7868,11 @@
         <f t="shared" si="9"/>
         <v>154.99193856146383</v>
       </c>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H265">
+        <v>259831</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A266" s="1">
         <v>41000</v>
       </c>
@@ -7098,8 +7896,11 @@
         <f t="shared" si="9"/>
         <v>137.38433244960231</v>
       </c>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H266">
+        <v>273904</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A267" s="1">
         <v>41030</v>
       </c>
@@ -7123,8 +7924,11 @@
         <f t="shared" si="9"/>
         <v>148.8629988213504</v>
       </c>
-    </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H267">
+        <v>313989</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A268" s="1">
         <v>41061</v>
       </c>
@@ -7148,8 +7952,11 @@
         <f t="shared" si="9"/>
         <v>137.71091177184138</v>
       </c>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H268">
+        <v>264399</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A269" s="1">
         <v>41091</v>
       </c>
@@ -7173,8 +7980,11 @@
         <f t="shared" si="9"/>
         <v>137.86295228479975</v>
       </c>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H269">
+        <v>286179</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A270" s="1">
         <v>41122</v>
       </c>
@@ -7198,8 +8008,11 @@
         <f t="shared" si="9"/>
         <v>137.96241396589903</v>
       </c>
-    </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H270">
+        <v>356967</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A271" s="1">
         <v>41153</v>
       </c>
@@ -7223,8 +8036,11 @@
         <f t="shared" si="9"/>
         <v>142.19171888581846</v>
       </c>
-    </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H271">
+        <v>316315</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A272" s="1">
         <v>41183</v>
       </c>
@@ -7248,8 +8064,11 @@
         <f t="shared" si="9"/>
         <v>140.42682815872487</v>
       </c>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H272">
+        <v>347337</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A273" s="1">
         <v>41214</v>
       </c>
@@ -7273,8 +8092,11 @@
         <f t="shared" si="9"/>
         <v>131.81927122826022</v>
       </c>
-    </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H273">
+        <v>306711</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A274" s="1">
         <v>41244</v>
       </c>
@@ -7298,8 +8120,11 @@
         <f t="shared" si="9"/>
         <v>124.17005540046623</v>
       </c>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H274">
+        <v>357187</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A275" s="1">
         <v>41275</v>
       </c>
@@ -7323,8 +8148,11 @@
         <f t="shared" si="9"/>
         <v>141.11814674896243</v>
       </c>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H275">
+        <v>277349</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A276" s="1">
         <v>41306</v>
       </c>
@@ -7348,8 +8176,11 @@
         <f t="shared" si="9"/>
         <v>139.82685413416539</v>
       </c>
-    </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H276">
+        <v>258047</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A277" s="1">
         <v>41334</v>
       </c>
@@ -7373,8 +8204,11 @@
         <f t="shared" si="9"/>
         <v>148.13964778455824</v>
       </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H277">
+        <v>323715</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A278" s="1">
         <v>41365</v>
       </c>
@@ -7398,8 +8232,11 @@
         <f t="shared" si="9"/>
         <v>146.27563372057554</v>
       </c>
-    </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H278">
+        <v>311127</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A279" s="1">
         <v>41395</v>
       </c>
@@ -7423,8 +8260,11 @@
         <f t="shared" si="9"/>
         <v>139.9466349059602</v>
       </c>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H279">
+        <v>300902</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A280" s="1">
         <v>41426</v>
       </c>
@@ -7448,8 +8288,11 @@
         <f t="shared" si="9"/>
         <v>131.68148423878048</v>
       </c>
-    </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H280">
+        <v>274643</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A281" s="1">
         <v>41456</v>
       </c>
@@ -7473,8 +8316,11 @@
         <f t="shared" si="9"/>
         <v>133.411641353801</v>
       </c>
-    </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H281">
+        <v>296650</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A282" s="1">
         <v>41487</v>
       </c>
@@ -7498,8 +8344,11 @@
         <f t="shared" si="9"/>
         <v>126.94971507359791</v>
       </c>
-    </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H282">
+        <v>276454</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A283" s="1">
         <v>41518</v>
       </c>
@@ -7523,8 +8372,11 @@
         <f t="shared" si="9"/>
         <v>123.05457673003598</v>
       </c>
-    </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H283">
+        <v>326993</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A284" s="1">
         <v>41548</v>
       </c>
@@ -7548,8 +8400,11 @@
         <f t="shared" si="9"/>
         <v>116.43547204686632</v>
       </c>
-    </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H284">
+        <v>327002</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A285" s="1">
         <v>41579</v>
       </c>
@@ -7573,8 +8428,11 @@
         <f t="shared" si="9"/>
         <v>109.70085260261524</v>
       </c>
-    </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H285">
+        <v>246652</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A286" s="1">
         <v>41609</v>
       </c>
@@ -7598,8 +8456,11 @@
         <f t="shared" si="9"/>
         <v>104.98918476354297</v>
       </c>
-    </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H286">
+        <v>327970</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A287" s="1">
         <v>41640</v>
       </c>
@@ -7623,8 +8484,11 @@
         <f t="shared" si="9"/>
         <v>107.3433197577186</v>
       </c>
-    </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H287">
+        <v>298079</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A288" s="1">
         <v>41671</v>
       </c>
@@ -7648,8 +8512,11 @@
         <f t="shared" si="9"/>
         <v>105.59713583220096</v>
       </c>
-    </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H288">
+        <v>265990</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A289" s="1">
         <v>41699</v>
       </c>
@@ -7673,8 +8540,11 @@
         <f t="shared" si="9"/>
         <v>119.76487039034467</v>
       </c>
-    </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H289">
+        <v>244499</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A290" s="1">
         <v>41730</v>
       </c>
@@ -7698,8 +8568,11 @@
         <f t="shared" si="9"/>
         <v>122.03062352992109</v>
       </c>
-    </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H290">
+        <v>300138</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A291" s="1">
         <v>41760</v>
       </c>
@@ -7723,8 +8596,11 @@
         <f t="shared" si="9"/>
         <v>119.10006234133638</v>
       </c>
-    </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H291">
+        <v>292836</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A292" s="1">
         <v>41791</v>
       </c>
@@ -7748,8 +8624,11 @@
         <f t="shared" si="9"/>
         <v>123.31229665500365</v>
       </c>
-    </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H292">
+        <v>303415</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A293" s="1">
         <v>41821</v>
       </c>
@@ -7773,8 +8652,11 @@
         <f t="shared" si="9"/>
         <v>120.68281664944595</v>
       </c>
-    </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H293">
+        <v>332716</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A294" s="1">
         <v>41852</v>
       </c>
@@ -7798,8 +8680,11 @@
         <f t="shared" si="9"/>
         <v>118.74124505939092</v>
       </c>
-    </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H294">
+        <v>317641</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A295" s="1">
         <v>41883</v>
       </c>
@@ -7823,8 +8708,11 @@
         <f t="shared" si="9"/>
         <v>121.47554578064567</v>
       </c>
-    </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H295">
+        <v>326364</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A296" s="1">
         <v>41913</v>
       </c>
@@ -7848,8 +8736,11 @@
         <f t="shared" si="9"/>
         <v>120.66245723300588</v>
       </c>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H296">
+        <v>248568</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A297" s="1">
         <v>41944</v>
       </c>
@@ -7873,8 +8764,11 @@
         <f t="shared" si="9"/>
         <v>120.90528789682716</v>
       </c>
-    </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H297">
+        <v>208928</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A298" s="1">
         <v>41974</v>
       </c>
@@ -7898,8 +8792,11 @@
         <f t="shared" si="9"/>
         <v>120.64550156986718</v>
       </c>
-    </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H298">
+        <v>319846</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A299" s="1">
         <v>42005</v>
       </c>
@@ -7923,8 +8820,11 @@
         <f t="shared" si="9"/>
         <v>115.96475135878235</v>
       </c>
-    </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H299">
+        <v>216983</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A300" s="1">
         <v>42036</v>
       </c>
@@ -7948,8 +8848,11 @@
         <f t="shared" si="9"/>
         <v>116.34031198434775</v>
       </c>
-    </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H300">
+        <v>260763</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A301" s="1">
         <v>42064</v>
       </c>
@@ -7973,8 +8876,11 @@
         <f t="shared" si="9"/>
         <v>113.90907901832325</v>
       </c>
-    </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H301">
+        <v>313080</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A302" s="1">
         <v>42095</v>
       </c>
@@ -7998,8 +8904,11 @@
         <f t="shared" si="9"/>
         <v>110.5586799447417</v>
       </c>
-    </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H302">
+        <v>323780</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A303" s="1">
         <v>42125</v>
       </c>
@@ -8023,8 +8932,11 @@
         <f t="shared" si="9"/>
         <v>106.04925366994014</v>
       </c>
-    </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H303">
+        <v>296517</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A304" s="1">
         <v>42156</v>
       </c>
@@ -8048,8 +8960,11 @@
         <f t="shared" si="9"/>
         <v>113.41292095085484</v>
       </c>
-    </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H304">
+        <v>328768</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A305" s="1">
         <v>42186</v>
       </c>
@@ -8073,8 +8988,11 @@
         <f t="shared" si="9"/>
         <v>112.38809653891865</v>
       </c>
-    </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H305">
+        <v>328813</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A306" s="1">
         <v>42217</v>
       </c>
@@ -8098,8 +9016,11 @@
         <f t="shared" si="9"/>
         <v>109.79136212599418</v>
       </c>
-    </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H306">
+        <v>310231</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A307" s="1">
         <v>42248</v>
       </c>
@@ -8123,8 +9044,11 @@
         <f t="shared" si="9"/>
         <v>111.31542804492857</v>
       </c>
-    </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H307">
+        <v>278362</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A308" s="1">
         <v>42278</v>
       </c>
@@ -8148,8 +9072,11 @@
         <f t="shared" si="9"/>
         <v>106.78822198018372</v>
       </c>
-    </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H308">
+        <v>322367</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A309" s="1">
         <v>42309</v>
       </c>
@@ -8173,8 +9100,11 @@
         <f t="shared" si="9"/>
         <v>106.19657829094906</v>
       </c>
-    </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H309">
+        <v>256327</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A310" s="1">
         <v>42339</v>
       </c>
@@ -8198,8 +9128,11 @@
         <f t="shared" si="9"/>
         <v>100.52127240990582</v>
       </c>
-    </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H310">
+        <v>315031</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A311" s="1">
         <v>42370</v>
       </c>
@@ -8223,8 +9156,11 @@
         <f t="shared" si="9"/>
         <v>100.65875749577162</v>
       </c>
-    </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H311">
+        <v>268959</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A312" s="1">
         <v>42401</v>
       </c>
@@ -8248,8 +9184,11 @@
         <f t="shared" si="9"/>
         <v>106.30587408304253</v>
       </c>
-    </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H312">
+        <v>313358</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A313" s="1">
         <v>42430</v>
       </c>
@@ -8273,8 +9212,11 @@
         <f t="shared" si="9"/>
         <v>110.65025531845737</v>
       </c>
-    </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H313">
+        <v>330186</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A314" s="1">
         <v>42461</v>
       </c>
@@ -8298,8 +9240,11 @@
         <f t="shared" si="9"/>
         <v>109.83110919241538</v>
       </c>
-    </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H314">
+        <v>272495</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A315" s="1">
         <v>42491</v>
       </c>
@@ -8323,8 +9268,11 @@
         <f t="shared" si="9"/>
         <v>110.07567690524061</v>
       </c>
-    </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H315">
+        <v>297979</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A316" s="1">
         <v>42522</v>
       </c>
@@ -8348,8 +9296,11 @@
         <f t="shared" si="9"/>
         <v>110.41384872519889</v>
       </c>
-    </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H316">
+        <v>350841</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A317" s="1">
         <v>42552</v>
       </c>
@@ -8373,8 +9324,11 @@
         <f t="shared" si="9"/>
         <v>119.76047805847587</v>
       </c>
-    </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H317">
+        <v>315745</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A318" s="1">
         <v>42583</v>
       </c>
@@ -8398,8 +9352,11 @@
         <f t="shared" si="9"/>
         <v>131.43882941962823</v>
       </c>
-    </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H318">
+        <v>345109</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A319" s="1">
         <v>42614</v>
       </c>
@@ -8423,8 +9380,11 @@
         <f t="shared" si="9"/>
         <v>133.07880010496623</v>
       </c>
-    </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H319">
+        <v>368392</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A320" s="1">
         <v>42644</v>
       </c>
@@ -8448,8 +9408,11 @@
         <f t="shared" si="9"/>
         <v>133.89848036227465</v>
       </c>
-    </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H320">
+        <v>341758</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A321" s="1">
         <v>42675</v>
       </c>
@@ -8473,8 +9436,11 @@
         <f t="shared" si="9"/>
         <v>169.03825255371609</v>
       </c>
-    </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H321">
+        <v>321372</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A322" s="1">
         <v>42705</v>
       </c>
@@ -8498,8 +9464,11 @@
         <f t="shared" si="9"/>
         <v>165.95425749750839</v>
       </c>
-    </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H322">
+        <v>348556</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A323" s="1">
         <v>42736</v>
       </c>
@@ -8523,8 +9492,11 @@
         <f t="shared" ref="G323:G386" si="11">E323*1000/D323</f>
         <v>165.33488136807236</v>
       </c>
-    </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H323">
+        <v>192036</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A324" s="1">
         <v>42767</v>
       </c>
@@ -8548,8 +9520,11 @@
         <f t="shared" si="11"/>
         <v>176.30165889271956</v>
       </c>
-    </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H324">
+        <v>273920</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A325" s="1">
         <v>42795</v>
       </c>
@@ -8573,8 +9548,11 @@
         <f t="shared" si="11"/>
         <v>173.12283137787259</v>
       </c>
-    </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H325">
+        <v>375592</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A326" s="1">
         <v>42826</v>
       </c>
@@ -8598,8 +9576,11 @@
         <f t="shared" si="11"/>
         <v>168.94343880350235</v>
       </c>
-    </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H326">
+        <v>275399</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A327" s="1">
         <v>42856</v>
       </c>
@@ -8623,8 +9604,11 @@
         <f t="shared" si="11"/>
         <v>167.768224152735</v>
       </c>
-    </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H327">
+        <v>275522</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A328" s="1">
         <v>42887</v>
       </c>
@@ -8648,8 +9632,11 @@
         <f t="shared" si="11"/>
         <v>155.9061944946755</v>
       </c>
-    </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H328">
+        <v>294101</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A329" s="1">
         <v>42917</v>
       </c>
@@ -8673,8 +9660,11 @@
         <f t="shared" si="11"/>
         <v>155.50003847671667</v>
       </c>
-    </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H329">
+        <v>275530</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A330" s="1">
         <v>42948</v>
       </c>
@@ -8698,8 +9688,11 @@
         <f t="shared" si="11"/>
         <v>145.439239290004</v>
       </c>
-    </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H330">
+        <v>303492</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A331" s="1">
         <v>42979</v>
       </c>
@@ -8723,8 +9716,11 @@
         <f t="shared" si="11"/>
         <v>145.42696833503575</v>
       </c>
-    </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H331">
+        <v>284777</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A332" s="1">
         <v>43009</v>
       </c>
@@ -8748,8 +9744,11 @@
         <f t="shared" si="11"/>
         <v>144.3436966923237</v>
       </c>
-    </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H332">
+        <v>310190</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A333" s="1">
         <v>43040</v>
       </c>
@@ -8773,8 +9772,11 @@
         <f t="shared" si="11"/>
         <v>141.0357726562714</v>
       </c>
-    </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H333">
+        <v>242790</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A334" s="1">
         <v>43070</v>
       </c>
@@ -8798,8 +9800,11 @@
         <f t="shared" si="11"/>
         <v>138.32901133650267</v>
       </c>
-    </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H334">
+        <v>379559</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A335" s="1">
         <v>43101</v>
       </c>
@@ -8823,8 +9828,11 @@
         <f t="shared" si="11"/>
         <v>122.97797492163009</v>
       </c>
-    </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H335">
+        <v>185288</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A336" s="1">
         <v>43132</v>
       </c>
@@ -8848,8 +9856,11 @@
         <f t="shared" si="11"/>
         <v>127.92636925509362</v>
       </c>
-    </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H336">
+        <v>274681</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A337" s="1">
         <v>43160</v>
       </c>
@@ -8873,8 +9884,11 @@
         <f t="shared" si="11"/>
         <v>107.85357542264377</v>
       </c>
-    </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H337">
+        <v>382671</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A338" s="1">
         <v>43191</v>
       </c>
@@ -8898,8 +9912,11 @@
         <f t="shared" si="11"/>
         <v>114.77843817638369</v>
       </c>
-    </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H338">
+        <v>302937</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A339" s="1">
         <v>43221</v>
       </c>
@@ -8923,8 +9940,11 @@
         <f t="shared" si="11"/>
         <v>104.43877823298514</v>
       </c>
-    </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H339">
+        <v>241284</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A340" s="1">
         <v>43252</v>
       </c>
@@ -8948,8 +9968,11 @@
         <f t="shared" si="11"/>
         <v>99.253779354793281</v>
       </c>
-    </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H340">
+        <v>312486</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A341" s="1">
         <v>43282</v>
       </c>
@@ -8973,8 +9996,11 @@
         <f t="shared" si="11"/>
         <v>101.39218350836586</v>
       </c>
-    </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H341">
+        <v>338542</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A342" s="1">
         <v>43313</v>
       </c>
@@ -8998,8 +10024,11 @@
         <f t="shared" si="11"/>
         <v>99.613276040672545</v>
       </c>
-    </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H342">
+        <v>379883</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A343" s="1">
         <v>43344</v>
       </c>
@@ -9023,8 +10052,11 @@
         <f t="shared" si="11"/>
         <v>92.100064793042193</v>
       </c>
-    </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H343">
+        <v>307878</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A344" s="1">
         <v>43374</v>
       </c>
@@ -9048,8 +10080,11 @@
         <f t="shared" si="11"/>
         <v>91.815621058508199</v>
       </c>
-    </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H344">
+        <v>326211</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A345" s="1">
         <v>43405</v>
       </c>
@@ -9073,8 +10108,11 @@
         <f t="shared" si="11"/>
         <v>96.663742030302899</v>
       </c>
-    </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H345">
+        <v>302813</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A346" s="1">
         <v>43435</v>
       </c>
@@ -9098,8 +10136,11 @@
         <f t="shared" si="11"/>
         <v>95.798794323289499</v>
       </c>
-    </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H346">
+        <v>372787</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A347" s="1">
         <v>43466</v>
       </c>
@@ -9123,8 +10164,11 @@
         <f t="shared" si="11"/>
         <v>91.466561360874849</v>
       </c>
-    </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H347">
+        <v>244684</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A348" s="1">
         <v>43497</v>
       </c>
@@ -9148,8 +10192,11 @@
         <f t="shared" si="11"/>
         <v>89.971656816177131</v>
       </c>
-    </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H348">
+        <v>310465</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A349" s="1">
         <v>43525</v>
       </c>
@@ -9173,8 +10220,11 @@
         <f t="shared" si="11"/>
         <v>90.090720190695734</v>
       </c>
-    </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H349">
+        <v>366311</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A350" s="1">
         <v>43556</v>
       </c>
@@ -9198,8 +10248,11 @@
         <f t="shared" si="11"/>
         <v>90.222194233081368</v>
       </c>
-    </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H350">
+        <v>318296</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A351" s="1">
         <v>43586</v>
       </c>
@@ -9223,8 +10276,11 @@
         <f t="shared" si="11"/>
         <v>81.971015369579135</v>
       </c>
-    </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H351">
+        <v>396854</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A352" s="1">
         <v>43617</v>
       </c>
@@ -9248,8 +10304,11 @@
         <f t="shared" si="11"/>
         <v>81.409173723350222</v>
       </c>
-    </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H352">
+        <v>358811</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A353" s="1">
         <v>43647</v>
       </c>
@@ -9273,8 +10332,11 @@
         <f t="shared" si="11"/>
         <v>82.2434572965211</v>
       </c>
-    </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H353">
+        <v>347971</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A354" s="1">
         <v>43678</v>
       </c>
@@ -9298,8 +10360,11 @@
         <f t="shared" si="11"/>
         <v>81.863171488297041</v>
       </c>
-    </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H354">
+        <v>334714</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A355" s="1">
         <v>43709</v>
       </c>
@@ -9323,8 +10388,11 @@
         <f t="shared" si="11"/>
         <v>80.257755281436445</v>
       </c>
-    </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H355">
+        <v>346098</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A356" s="1">
         <v>43739</v>
       </c>
@@ -9348,8 +10416,11 @@
         <f t="shared" si="11"/>
         <v>80.273503560829212</v>
       </c>
-    </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H356">
+        <v>342760</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A357" s="1">
         <v>43770</v>
       </c>
@@ -9373,8 +10444,11 @@
         <f t="shared" si="11"/>
         <v>81.617264806057193</v>
       </c>
-    </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H357">
+        <v>318833</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A358" s="1">
         <v>43800</v>
       </c>
@@ -9398,8 +10472,11 @@
         <f t="shared" si="11"/>
         <v>83.990418014704829</v>
       </c>
-    </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H358">
+        <v>315312</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A359" s="1">
         <v>43831</v>
       </c>
@@ -9423,8 +10500,11 @@
         <f t="shared" si="11"/>
         <v>83.157125560698404</v>
       </c>
-    </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H359">
+        <v>325394</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A360" s="1">
         <v>43862</v>
       </c>
@@ -9448,8 +10528,11 @@
         <f t="shared" si="11"/>
         <v>83.43258093693612</v>
       </c>
-    </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H360">
+        <v>310029</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A361" s="1">
         <v>43891</v>
       </c>
@@ -9473,8 +10556,11 @@
         <f t="shared" si="11"/>
         <v>81.544330743443112</v>
       </c>
-    </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H361">
+        <v>338639</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A362" s="1">
         <v>43922</v>
       </c>
@@ -9498,8 +10584,11 @@
         <f t="shared" si="11"/>
         <v>77.483616602725021</v>
       </c>
-    </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H362">
+        <v>371922</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A363" s="1">
         <v>43952</v>
       </c>
@@ -9523,8 +10612,11 @@
         <f t="shared" si="11"/>
         <v>74.436487974005857</v>
       </c>
-    </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H363">
+        <v>335163</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A364" s="1">
         <v>43983</v>
       </c>
@@ -9548,8 +10640,11 @@
         <f t="shared" si="11"/>
         <v>74.192974085640273</v>
       </c>
-    </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H364">
+        <v>353432</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A365" s="1">
         <v>44013</v>
       </c>
@@ -9573,8 +10668,11 @@
         <f t="shared" si="11"/>
         <v>74.576800146376939</v>
       </c>
-    </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H365">
+        <v>371171</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A366" s="1">
         <v>44044</v>
       </c>
@@ -9598,8 +10696,11 @@
         <f t="shared" si="11"/>
         <v>75.991850800396776</v>
       </c>
-    </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H366">
+        <v>329956</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A367" s="1">
         <v>44075</v>
       </c>
@@ -9623,8 +10724,11 @@
         <f t="shared" si="11"/>
         <v>77.235890437289768</v>
       </c>
-    </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H367">
+        <v>328171</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A368" s="1">
         <v>44105</v>
       </c>
@@ -9648,8 +10752,11 @@
         <f t="shared" si="11"/>
         <v>79.938421209242222</v>
       </c>
-    </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H368">
+        <v>333558</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A369" s="1">
         <v>44136</v>
       </c>
@@ -9673,8 +10780,11 @@
         <f t="shared" si="11"/>
         <v>80.172890697841211</v>
       </c>
-    </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H369">
+        <v>353642</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A370" s="1">
         <v>44166</v>
       </c>
@@ -9698,8 +10808,11 @@
         <f t="shared" si="11"/>
         <v>81.062977014036136</v>
       </c>
-    </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H370">
+        <v>380266</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A371" s="1">
         <v>44197</v>
       </c>
@@ -9723,8 +10836,11 @@
         <f t="shared" si="11"/>
         <v>84.320383003670273</v>
       </c>
-    </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H371">
+        <v>275879</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A372" s="1">
         <v>44228</v>
       </c>
@@ -9748,8 +10864,11 @@
         <f t="shared" si="11"/>
         <v>85.404618332169761</v>
       </c>
-    </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H372">
+        <v>308645</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A373" s="1">
         <v>44256</v>
       </c>
@@ -9773,8 +10892,11 @@
         <f t="shared" si="11"/>
         <v>85.441774610357541</v>
       </c>
-    </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H373">
+        <v>382348</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A374" s="1">
         <v>44287</v>
       </c>
@@ -9798,8 +10920,11 @@
         <f t="shared" si="11"/>
         <v>89.835166855001788</v>
       </c>
-    </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H374">
+        <v>312752</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A375" s="1">
         <v>44317</v>
       </c>
@@ -9823,8 +10948,11 @@
         <f t="shared" si="11"/>
         <v>87.285768940778283</v>
       </c>
-    </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H375">
+        <v>279416</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A376" s="1">
         <v>44348</v>
       </c>
@@ -9848,8 +10976,11 @@
         <f t="shared" si="11"/>
         <v>86.519584878543938</v>
       </c>
-    </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H376">
+        <v>297953</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A377" s="1">
         <v>44378</v>
       </c>
@@ -9873,8 +11004,11 @@
         <f t="shared" si="11"/>
         <v>90.152882395329698</v>
       </c>
-    </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H377">
+        <v>331043</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A378" s="1">
         <v>44409</v>
       </c>
@@ -9898,8 +11032,11 @@
         <f t="shared" si="11"/>
         <v>100.30350124815236</v>
       </c>
-    </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H378">
+        <v>353840</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A379" s="1">
         <v>44440</v>
       </c>
@@ -9923,8 +11060,11 @@
         <f t="shared" si="11"/>
         <v>109.08711775381823</v>
       </c>
-    </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H379">
+        <v>361187</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A380" s="1">
         <v>44470</v>
       </c>
@@ -9948,8 +11088,11 @@
         <f t="shared" si="11"/>
         <v>114.40054809735848</v>
       </c>
-    </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H380">
+        <v>312806</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A381" s="1">
         <v>44501</v>
       </c>
@@ -9973,8 +11116,11 @@
         <f t="shared" si="11"/>
         <v>128.16633056701286</v>
       </c>
-    </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H381">
+        <v>360421</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A382" s="1">
         <v>44531</v>
       </c>
@@ -9998,8 +11144,11 @@
         <f t="shared" si="11"/>
         <v>130.25174215542063</v>
       </c>
-    </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H382">
+        <v>456506</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A383" s="1">
         <v>44562</v>
       </c>
@@ -10023,8 +11172,11 @@
         <f t="shared" si="11"/>
         <v>155.01740793413924</v>
       </c>
-    </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H383">
+        <v>320429</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A384" s="1">
         <v>44593</v>
       </c>
@@ -10048,8 +11200,11 @@
         <f t="shared" si="11"/>
         <v>152.91073202923116</v>
       </c>
-    </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H384">
+        <v>297500</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A385" s="1">
         <v>44621</v>
       </c>
@@ -10073,8 +11228,11 @@
         <f t="shared" si="11"/>
         <v>155.26160569360391</v>
       </c>
-    </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H385">
+        <v>358963</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A386" s="1">
         <v>44652</v>
       </c>
@@ -10098,8 +11256,11 @@
         <f t="shared" si="11"/>
         <v>155.8956508618879</v>
       </c>
-    </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H386">
+        <v>252894</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A387" s="1">
         <v>44682</v>
       </c>
@@ -10123,8 +11284,11 @@
         <f t="shared" ref="G387:G437" si="13">E387*1000/D387</f>
         <v>159.49185848899143</v>
       </c>
-    </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H387">
+        <v>298588</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A388" s="1">
         <v>44713</v>
       </c>
@@ -10148,8 +11312,11 @@
         <f t="shared" si="13"/>
         <v>153.07310134199707</v>
       </c>
-    </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H388">
+        <v>350973</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A389" s="1">
         <v>44743</v>
       </c>
@@ -10173,8 +11340,11 @@
         <f t="shared" si="13"/>
         <v>149.54524996751894</v>
       </c>
-    </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H389">
+        <v>314000</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A390" s="1">
         <v>44774</v>
       </c>
@@ -10198,8 +11368,11 @@
         <f t="shared" si="13"/>
         <v>153.17007715317976</v>
       </c>
-    </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H390">
+        <v>320785</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A391" s="1">
         <v>44805</v>
       </c>
@@ -10223,8 +11396,11 @@
         <f t="shared" si="13"/>
         <v>156.47747203803496</v>
       </c>
-    </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H391">
+        <v>315388</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A392" s="1">
         <v>44835</v>
       </c>
@@ -10248,8 +11424,11 @@
         <f t="shared" si="13"/>
         <v>160.66345339483752</v>
       </c>
-    </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H392">
+        <v>293474</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A393" s="1">
         <v>44866</v>
       </c>
@@ -10273,8 +11452,11 @@
         <f t="shared" si="13"/>
         <v>162.88846347515474</v>
       </c>
-    </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H393">
+        <v>278350</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A394" s="1">
         <v>44896</v>
       </c>
@@ -10298,8 +11480,11 @@
         <f t="shared" si="13"/>
         <v>141.58691476319524</v>
       </c>
-    </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H394">
+        <v>337107</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A395" s="1">
         <v>44927</v>
       </c>
@@ -10323,8 +11508,11 @@
         <f t="shared" si="13"/>
         <v>141.05854534428434</v>
       </c>
-    </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H395">
+        <v>315398</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A396" s="1">
         <v>44958</v>
       </c>
@@ -10348,8 +11536,11 @@
         <f t="shared" si="13"/>
         <v>133.39469439999999</v>
       </c>
-    </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H396">
+        <v>280295</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A397" s="1">
         <v>44986</v>
       </c>
@@ -10373,8 +11564,11 @@
         <f t="shared" si="13"/>
         <v>146.31960043629448</v>
       </c>
-    </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H397">
+        <v>299325</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A398" s="1">
         <v>45017</v>
       </c>
@@ -10398,8 +11592,11 @@
         <f t="shared" si="13"/>
         <v>144.86726712075102</v>
       </c>
-    </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H398">
+        <v>315280</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A399" s="1">
         <v>45047</v>
       </c>
@@ -10423,8 +11620,11 @@
         <f t="shared" si="13"/>
         <v>142.70285369317105</v>
       </c>
-    </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H399">
+        <v>311497</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A400" s="1">
         <v>45078</v>
       </c>
@@ -10448,8 +11648,11 @@
         <f t="shared" si="13"/>
         <v>147.34877279445868</v>
       </c>
-    </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H400">
+        <v>331201</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A401" s="1">
         <v>45108</v>
       </c>
@@ -10473,8 +11676,11 @@
         <f t="shared" si="13"/>
         <v>152.86592252799142</v>
       </c>
-    </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H401">
+        <v>308693</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A402" s="1">
         <v>45139</v>
       </c>
@@ -10498,8 +11704,11 @@
         <f t="shared" si="13"/>
         <v>152.76063590516972</v>
       </c>
-    </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H402">
+        <v>335375</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A403" s="1">
         <v>45170</v>
       </c>
@@ -10523,8 +11732,11 @@
         <f t="shared" si="13"/>
         <v>154.89717822259107</v>
       </c>
-    </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H403">
+        <v>276870</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A404" s="1">
         <v>45200</v>
       </c>
@@ -10548,8 +11760,11 @@
         <f t="shared" si="13"/>
         <v>152.35343290864179</v>
       </c>
-    </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H404">
+        <v>279095</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A405" s="1">
         <v>45231</v>
       </c>
@@ -10573,8 +11788,11 @@
         <f t="shared" si="13"/>
         <v>143.05185308988703</v>
       </c>
-    </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H405">
+        <v>237309</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A406" s="1">
         <v>45261</v>
       </c>
@@ -10598,8 +11816,11 @@
         <f t="shared" si="13"/>
         <v>145.57158635255556</v>
       </c>
-    </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H406">
+        <v>331743</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A407" s="1">
         <v>45292</v>
       </c>
@@ -10623,8 +11844,11 @@
         <f t="shared" si="13"/>
         <v>155.48773342264479</v>
       </c>
-    </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H407">
+        <v>292918</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A408" s="1">
         <v>45323</v>
       </c>
@@ -10648,8 +11872,11 @@
         <f t="shared" si="13"/>
         <v>173.92829768689211</v>
       </c>
-    </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H408">
+        <v>257235</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A409" s="1">
         <v>45352</v>
       </c>
@@ -10673,8 +11900,11 @@
         <f t="shared" si="13"/>
         <v>178.58815083512161</v>
       </c>
-    </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H409">
+        <v>355841</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A410" s="1">
         <v>45383</v>
       </c>
@@ -10698,8 +11928,11 @@
         <f t="shared" si="13"/>
         <v>185.9501930502627</v>
       </c>
-    </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H410">
+        <v>343082</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A411" s="1">
         <v>45413</v>
       </c>
@@ -10723,8 +11956,11 @@
         <f t="shared" si="13"/>
         <v>198.21581505662544</v>
       </c>
-    </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H411">
+        <v>379555</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A412" s="1">
         <v>45444</v>
       </c>
@@ -10748,8 +11984,11 @@
         <f t="shared" si="13"/>
         <v>211.13237240056475</v>
       </c>
-    </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H412">
+        <v>289866</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A413" s="1">
         <v>45474</v>
       </c>
@@ -10773,8 +12012,11 @@
         <f t="shared" si="13"/>
         <v>217.99421700174048</v>
       </c>
-    </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H413">
+        <v>370696</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A414" s="1">
         <v>45505</v>
       </c>
@@ -10798,8 +12040,11 @@
         <f t="shared" si="13"/>
         <v>221.03144927606775</v>
       </c>
-    </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H414">
+        <v>320109</v>
+      </c>
+    </row>
+    <row r="415" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A415" s="1">
         <v>45536</v>
       </c>
@@ -10823,8 +12068,11 @@
         <f t="shared" si="13"/>
         <v>238.03325019387921</v>
       </c>
-    </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H415">
+        <v>362889</v>
+      </c>
+    </row>
+    <row r="416" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A416" s="1">
         <v>45566</v>
       </c>
@@ -10848,8 +12096,11 @@
         <f t="shared" si="13"/>
         <v>250.98543062945959</v>
       </c>
-    </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H416">
+        <v>356604</v>
+      </c>
+    </row>
+    <row r="417" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A417" s="1">
         <v>45597</v>
       </c>
@@ -10873,8 +12124,11 @@
         <f t="shared" si="13"/>
         <v>253.73440014968077</v>
       </c>
-    </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H417">
+        <v>373699</v>
+      </c>
+    </row>
+    <row r="418" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A418" s="1">
         <v>45627</v>
       </c>
@@ -10898,8 +12152,11 @@
         <f t="shared" si="13"/>
         <v>252.06421100554377</v>
       </c>
-    </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H418">
+        <v>424248</v>
+      </c>
+    </row>
+    <row r="419" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A419" s="1">
         <v>45658</v>
       </c>
@@ -10923,8 +12180,11 @@
         <f t="shared" si="13"/>
         <v>266.59951865512687</v>
       </c>
-    </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H419">
+        <v>366225</v>
+      </c>
+    </row>
+    <row r="420" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A420" s="1">
         <v>45689</v>
       </c>
@@ -10948,8 +12208,11 @@
         <f t="shared" si="13"/>
         <v>299.60289247568085</v>
       </c>
-    </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H420">
+        <v>281880</v>
+      </c>
+    </row>
+    <row r="421" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A421" s="1">
         <v>45717</v>
       </c>
@@ -10973,8 +12236,11 @@
         <f t="shared" si="13"/>
         <v>317.92754104257494</v>
       </c>
-    </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H421">
+        <v>330097</v>
+      </c>
+    </row>
+    <row r="422" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A422" s="1">
         <v>45748</v>
       </c>
@@ -10998,8 +12264,11 @@
         <f t="shared" si="13"/>
         <v>345.1028795177275</v>
       </c>
-    </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H422">
+        <v>306689</v>
+      </c>
+    </row>
+    <row r="423" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A423" s="1">
         <v>45778</v>
       </c>
@@ -11023,8 +12292,11 @@
         <f t="shared" si="13"/>
         <v>327.41131437427259</v>
       </c>
-    </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H423">
+        <v>358301</v>
+      </c>
+    </row>
+    <row r="424" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A424" s="1">
         <v>45809</v>
       </c>
@@ -11048,8 +12320,11 @@
         <f t="shared" si="13"/>
         <v>291.28684936693213</v>
       </c>
-    </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H424">
+        <v>305096</v>
+      </c>
+    </row>
+    <row r="425" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A425" s="1">
         <v>45839</v>
       </c>
@@ -11073,8 +12348,11 @@
         <f t="shared" si="13"/>
         <v>265.84977306255081</v>
       </c>
-    </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H425">
+        <v>294842</v>
+      </c>
+    </row>
+    <row r="426" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A426" s="1">
         <v>45870</v>
       </c>
@@ -11098,8 +12376,11 @@
         <f t="shared" si="13"/>
         <v>245.64918421861162</v>
       </c>
-    </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H426">
+        <v>267166</v>
+      </c>
+    </row>
+    <row r="427" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A427" s="1">
         <v>45901</v>
       </c>
@@ -11123,8 +12404,11 @@
         <f t="shared" si="13"/>
         <v>243.68972186269062</v>
       </c>
-    </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H427">
+        <v>302178</v>
+      </c>
+    </row>
+    <row r="428" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A428" s="1">
         <v>45931</v>
       </c>
@@ -11148,8 +12432,11 @@
         <f t="shared" si="13"/>
         <v>247.18847914797706</v>
       </c>
-    </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H428">
+        <v>306474</v>
+      </c>
+    </row>
+    <row r="429" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A429" s="1">
         <v>45962</v>
       </c>
@@ -11173,8 +12460,11 @@
         <f t="shared" si="13"/>
         <v>262.76960936515468</v>
       </c>
-    </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H429">
+        <v>294793</v>
+      </c>
+    </row>
+    <row r="430" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A430" s="1">
         <v>45992</v>
       </c>
@@ -11198,8 +12488,11 @@
         <f t="shared" si="13"/>
         <v>270.34069800492466</v>
       </c>
-    </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H430">
+        <v>279778</v>
+      </c>
+    </row>
+    <row r="431" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A431" s="1">
         <v>46023</v>
       </c>
@@ -11223,8 +12516,11 @@
         <f t="shared" si="13"/>
         <v>259.47909244066403</v>
       </c>
-    </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H431">
+        <v>252638</v>
+      </c>
+    </row>
+    <row r="432" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A432" s="1">
         <v>46054</v>
       </c>
@@ -11248,8 +12544,11 @@
         <f t="shared" si="13"/>
         <v>253.83161783522374</v>
       </c>
-    </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H432">
+        <v>329278</v>
+      </c>
+    </row>
+    <row r="433" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A433" s="1">
         <v>46082</v>
       </c>
@@ -11273,8 +12572,11 @@
         <f t="shared" si="13"/>
         <v>233.55231687298388</v>
       </c>
-    </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H433">
+        <v>395164</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A434" s="1">
         <v>46113</v>
       </c>
@@ -11298,8 +12600,11 @@
         <f t="shared" si="13"/>
         <v>222.7170544851148</v>
       </c>
-    </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H434">
+        <v>375445</v>
+      </c>
+    </row>
+    <row r="435" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A435" s="1">
         <v>46143</v>
       </c>
@@ -11323,8 +12628,11 @@
         <f t="shared" si="13"/>
         <v>218.28556656992197</v>
       </c>
-    </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H435">
+        <v>358477</v>
+      </c>
+    </row>
+    <row r="436" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A436" s="1">
         <v>46174</v>
       </c>
@@ -11348,8 +12656,11 @@
         <f t="shared" si="13"/>
         <v>211.23722391825487</v>
       </c>
-    </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="H436">
+        <v>423421</v>
+      </c>
+    </row>
+    <row r="437" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A437" s="1">
         <v>46204</v>
       </c>
@@ -11372,6 +12683,9 @@
       <c r="G437" s="3">
         <f t="shared" si="13"/>
         <v>208.35008992604864</v>
+      </c>
+      <c r="H437">
+        <v>351403</v>
       </c>
     </row>
   </sheetData>
@@ -11380,6 +12694,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bb8a688-9fce-46e7-b438-b3767c5bce2d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4315a1d7-5b2b-4aec-b3c1-bed157ad3cff">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010069BD0CCD6E02B74F9DAE55BEF75C7D8B" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="755c61f92718ec80af2f84face8369ae">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4315a1d7-5b2b-4aec-b3c1-bed157ad3cff" xmlns:ns3="3bb8a688-9fce-46e7-b438-b3767c5bce2d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6db04e3886905a89fbc2397dfd3aa562" ns2:_="" ns3:_="">
     <xsd:import namespace="4315a1d7-5b2b-4aec-b3c1-bed157ad3cff"/>
@@ -11568,36 +12902,42 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bb8a688-9fce-46e7-b438-b3767c5bce2d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4315a1d7-5b2b-4aec-b3c1-bed157ad3cff">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA960A0D-7ED3-46E2-9A33-FC2E33C71E48}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4C87030-C7DC-4CD4-BF18-E565629AADD6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3bb8a688-9fce-46e7-b438-b3767c5bce2d"/>
+    <ds:schemaRef ds:uri="4315a1d7-5b2b-4aec-b3c1-bed157ad3cff"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B22B5601-BD39-4ACC-8618-CD70758097C8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B22B5601-BD39-4ACC-8618-CD70758097C8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4C87030-C7DC-4CD4-BF18-E565629AADD6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA960A0D-7ED3-46E2-9A33-FC2E33C71E48}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4315a1d7-5b2b-4aec-b3c1-bed157ad3cff"/>
+    <ds:schemaRef ds:uri="3bb8a688-9fce-46e7-b438-b3767c5bce2d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
